--- a/diseases/d169/2000-2004.xlsx
+++ b/diseases/d169/2000-2004.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1788,6 +1823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2223,6 +2273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2368,6 +2423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2513,6 +2573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3818,6 +3923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3963,6 +4073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4108,6 +4223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4253,6 +4373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4398,6 +4523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4543,6 +4673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4688,6 +4823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4833,6 +4973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4978,6 +5123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5123,6 +5273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5268,6 +5423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5413,6 +5573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5558,6 +5723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5703,6 +5873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5851,6 +6026,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5996,6 +6176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6144,6 +6329,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6289,6 +6479,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6437,6 +6632,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6582,6 +6782,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6727,6 +6932,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6875,6 +7085,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7020,6 +7235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7168,6 +7388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7313,6 +7538,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7461,6 +7691,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7606,6 +7841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7754,6 +7994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7899,6 +8144,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8047,6 +8297,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8192,6 +8447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8340,6 +8600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8485,6 +8750,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8633,6 +8903,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8778,6 +9053,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8926,6 +9206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9071,6 +9356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9219,6 +9509,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9364,6 +9659,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9510,6 +9810,11 @@
       <c r="S62" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">

--- a/diseases/d169/2000-2004.xlsx
+++ b/diseases/d169/2000-2004.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0.002125693624458129</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,11 +903,6 @@
       <c r="R3" t="n">
         <v>0.002125693624458129</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,22 +915,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1068,11 +1038,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1218,11 +1173,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,22 +1185,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1368,11 +1308,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,22 +1320,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1518,11 +1443,6 @@
       <c r="R7" t="n">
         <v>0.002125693624458129</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1535,22 +1455,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1668,11 +1578,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1685,22 +1590,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1818,11 +1713,6 @@
       <c r="R9" t="n">
         <v>0.006377080873374387</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1835,22 +1725,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1968,11 +1848,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1985,22 +1860,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2118,11 +1983,6 @@
       <c r="R11" t="n">
         <v>0.008502774497832516</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2135,22 +1995,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2268,11 +2118,6 @@
       <c r="R12" t="n">
         <v>0.01275416174674877</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2285,22 +2130,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2418,11 +2253,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2435,22 +2265,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2568,11 +2388,6 @@
       <c r="R14" t="n">
         <v>0.004228408433091266</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2585,22 +2400,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2718,11 +2523,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2735,22 +2535,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2868,11 +2658,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2885,22 +2670,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3018,11 +2793,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3035,22 +2805,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3168,11 +2928,6 @@
       <c r="R18" t="n">
         <v>0.004228408433091266</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3185,22 +2940,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3318,11 +3063,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,22 +3075,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3468,11 +3198,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3485,22 +3210,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3618,11 +3333,6 @@
       <c r="R21" t="n">
         <v>0.002114204216545633</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3635,22 +3345,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3768,11 +3468,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3785,22 +3480,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3918,11 +3603,6 @@
       <c r="R23" t="n">
         <v>0.002114204216545633</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3935,22 +3615,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4068,11 +3738,6 @@
       <c r="R24" t="n">
         <v>0.004228408433091266</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4085,22 +3750,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4218,11 +3873,6 @@
       <c r="R25" t="n">
         <v>0.002114204216545633</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4235,22 +3885,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4368,11 +4008,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4385,22 +4020,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4518,11 +4143,6 @@
       <c r="R27" t="n">
         <v>0.002104635732751713</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4535,22 +4155,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4668,11 +4278,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4685,22 +4290,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4818,11 +4413,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4835,22 +4425,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4968,11 +4548,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4985,22 +4560,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5118,11 +4683,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5135,22 +4695,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5268,11 +4818,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5285,22 +4830,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5418,11 +4953,6 @@
       <c r="R33" t="n">
         <v>0.002104635732751713</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5435,22 +4965,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5568,11 +5088,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5585,22 +5100,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5718,11 +5223,6 @@
       <c r="R35" t="n">
         <v>0.004209271465503426</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5735,22 +5235,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5868,11 +5358,6 @@
       <c r="R36" t="n">
         <v>0.008418542931006853</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5885,22 +5370,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6021,11 +5496,6 @@
       <c r="R37" t="n">
         <v>0.004412259560257887</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6038,22 +5508,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6171,11 +5631,6 @@
       <c r="R38" t="n">
         <v>0.002104635732751713</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6188,22 +5643,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6324,11 +5769,6 @@
       <c r="R39" t="n">
         <v>0.01764903824103155</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6341,22 +5781,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6474,11 +5904,6 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6491,22 +5916,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6627,11 +6042,6 @@
       <c r="R41" t="n">
         <v>0.02198243682434508</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6644,22 +6054,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6777,11 +6177,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6794,22 +6189,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6927,11 +6312,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6944,22 +6324,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7080,11 +6450,6 @@
       <c r="R44" t="n">
         <v>0.01318946209460705</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7097,22 +6462,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7230,11 +6585,6 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7247,22 +6597,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7383,11 +6723,6 @@
       <c r="R46" t="n">
         <v>0.004396487364869015</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7400,22 +6735,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7533,11 +6858,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7550,22 +6870,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7686,11 +6996,6 @@
       <c r="R48" t="n">
         <v>0.04836136101355916</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7703,22 +7008,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7836,11 +7131,6 @@
       <c r="R49" t="n">
         <v>0.004193129199294409</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7853,22 +7143,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7989,11 +7269,6 @@
       <c r="R50" t="n">
         <v>0.02637892418921409</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8006,22 +7281,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8139,11 +7404,6 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8156,22 +7416,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8292,11 +7542,6 @@
       <c r="R52" t="n">
         <v>0.05715433574329719</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8309,22 +7554,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8442,11 +7677,6 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8459,22 +7689,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8595,11 +7815,6 @@
       <c r="R54" t="n">
         <v>0.03956838628382114</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8612,22 +7827,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8745,11 +7950,6 @@
       <c r="R55" t="n">
         <v>0.002096564599647205</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8762,22 +7962,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8898,11 +8088,6 @@
       <c r="R56" t="n">
         <v>0.03956838628382114</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8915,22 +8100,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9048,11 +8223,6 @@
       <c r="R57" t="n">
         <v>0.02096564599647205</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9065,22 +8235,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9201,11 +8361,6 @@
       <c r="R58" t="n">
         <v>0.03517189891895212</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9218,22 +8373,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9351,11 +8496,6 @@
       <c r="R59" t="n">
         <v>0.01048282299823602</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9368,22 +8508,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9504,11 +8634,6 @@
       <c r="R60" t="n">
         <v>0.01758594945947606</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9521,22 +8646,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9654,11 +8769,6 @@
       <c r="R61" t="n">
         <v>0.002096564599647205</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9671,22 +8781,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9807,11 +8907,6 @@
       <c r="R62" t="n">
         <v>0.008792974729738031</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9824,22 +8919,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>

--- a/diseases/d169/2000-2004.xlsx
+++ b/diseases/d169/2000-2004.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0.002125693624458129</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,12 +785,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -903,6 +918,11 @@
       <c r="R3" t="n">
         <v>0.002125693624458129</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,12 +935,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1038,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,12 +1085,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1173,6 +1218,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,12 +1235,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1308,6 +1368,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,12 +1385,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1443,6 +1518,11 @@
       <c r="R7" t="n">
         <v>0.002125693624458129</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1455,12 +1535,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1578,6 +1668,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1590,12 +1685,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1713,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0.006377080873374387</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1725,12 +1835,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1848,6 +1968,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1860,12 +1985,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -1983,6 +2118,11 @@
       <c r="R11" t="n">
         <v>0.008502774497832516</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1995,12 +2135,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2118,6 +2268,11 @@
       <c r="R12" t="n">
         <v>0.01275416174674877</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2130,12 +2285,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2253,6 +2418,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2265,12 +2435,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2388,6 +2568,11 @@
       <c r="R14" t="n">
         <v>0.004228408433091266</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2400,12 +2585,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2523,6 +2718,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2535,12 +2735,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2658,6 +2868,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2670,12 +2885,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2793,6 +3018,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2805,12 +3035,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2928,6 +3168,11 @@
       <c r="R18" t="n">
         <v>0.004228408433091266</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2940,12 +3185,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3063,6 +3318,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3075,12 +3335,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3198,6 +3468,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3210,12 +3485,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3333,6 +3618,11 @@
       <c r="R21" t="n">
         <v>0.002114204216545633</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3345,12 +3635,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3468,6 +3768,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3480,12 +3785,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3603,6 +3918,11 @@
       <c r="R23" t="n">
         <v>0.002114204216545633</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3615,12 +3935,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3738,6 +4068,11 @@
       <c r="R24" t="n">
         <v>0.004228408433091266</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3750,12 +4085,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -3873,6 +4218,11 @@
       <c r="R25" t="n">
         <v>0.002114204216545633</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3885,12 +4235,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4008,6 +4368,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4020,12 +4385,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4143,6 +4518,11 @@
       <c r="R27" t="n">
         <v>0.002104635732751713</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4155,12 +4535,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4278,6 +4668,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4290,12 +4685,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4413,6 +4818,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4425,12 +4835,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4548,6 +4968,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4560,12 +4985,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4683,6 +5118,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4695,12 +5135,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4818,6 +5268,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4830,12 +5285,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -4953,6 +5418,11 @@
       <c r="R33" t="n">
         <v>0.002104635732751713</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4965,12 +5435,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5088,6 +5568,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5100,12 +5585,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5223,6 +5718,11 @@
       <c r="R35" t="n">
         <v>0.004209271465503426</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5235,12 +5735,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5358,6 +5868,11 @@
       <c r="R36" t="n">
         <v>0.008418542931006853</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5370,12 +5885,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5631,6 +6156,11 @@
       <c r="R38" t="n">
         <v>0.002104635732751713</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5643,12 +6173,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5904,6 +6444,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5916,12 +6461,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6177,6 +6732,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6189,12 +6749,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6312,6 +6882,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6324,12 +6899,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6585,6 +7170,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6597,12 +7187,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6858,6 +7458,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6870,12 +7475,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7131,6 +7746,11 @@
       <c r="R49" t="n">
         <v>0.004193129199294409</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7143,12 +7763,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7404,6 +8034,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7416,12 +8051,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7677,6 +8322,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7689,12 +8339,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -7950,6 +8610,11 @@
       <c r="R55" t="n">
         <v>0.002096564599647205</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7962,12 +8627,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8223,6 +8898,11 @@
       <c r="R57" t="n">
         <v>0.02096564599647205</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8235,12 +8915,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8496,6 +9186,11 @@
       <c r="R59" t="n">
         <v>0.01048282299823602</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8508,12 +9203,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8769,6 +9474,11 @@
       <c r="R61" t="n">
         <v>0.002096564599647205</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8781,12 +9491,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
